--- a/output/details/2026-05-10/preprocessed_data.xlsx
+++ b/output/details/2026-05-10/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46152</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1080747272572554</v>
+        <v>-0.1077177417899793</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2007135120226239</v>
+        <v>-0.1302098102710439</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2004237893165086</v>
+        <v>-0.1299500958879619</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1329203955405532</v>
+        <v>0.0141169696034501</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703684635496489</v>
+        <v>0.001703963774245856</v>
       </c>
       <c r="G2" t="n">
-        <v>1.777639767396541</v>
+        <v>2.352573801774779</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4610075097584335</v>
+        <v>-0.2571187381181742</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
